--- a/Determinantes/Tabelas/dicionário_determinantes.xlsx
+++ b/Determinantes/Tabelas/dicionário_determinantes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iasmi\OneDrive\Documentos\GitHub\Epidynamics\Determinantes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iasmi\OneDrive\Documentos\GitHub\Epidynamics\Determinantes\Tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C41CFA-FEB7-4EED-8A17-3ABF8511BC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AC3640-EAB5-4312-AF2F-BB08792E2619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="11111" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="56">
   <si>
     <t>Sigla</t>
   </si>
@@ -179,6 +179,30 @@
   </si>
   <si>
     <t>Representa a proporção de acesso à abastecimento de água dentro da moradia.</t>
+  </si>
+  <si>
+    <t>são o número de dias no ano que a umidade foi maior que 60%</t>
+  </si>
+  <si>
+    <t>são o número de dias no ano que a temperatura foi maior que 20°</t>
+  </si>
+  <si>
+    <t>são o número de dias no ano que a precipitação foi maior que 10mm</t>
+  </si>
+  <si>
+    <t>thr_temp</t>
+  </si>
+  <si>
+    <t>thr_umid</t>
+  </si>
+  <si>
+    <t>são o número de dias no ano que a umidade foi maior que 60% e a temperatura maior do que 20°</t>
+  </si>
+  <si>
+    <t>thr_temp_umid</t>
+  </si>
+  <si>
+    <t>thr_prec</t>
   </si>
 </sst>
 </file>
@@ -490,7 +514,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -561,150 +585,190 @@
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>42</v>
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>43</v>
+      <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="4"/>
+      <c r="A10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="A11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G11" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="G12" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="G15" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="G16" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
